--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/phi-4/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/phi-4/metrics_default_vs_aae.xlsx
@@ -420,7 +420,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.45</v>
+        <v>0.4428571428571428</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -429,16 +429,16 @@
         <v>0.4507042253521127</v>
       </c>
       <c r="D2">
-        <v>0.5531914893617021</v>
+        <v>0.5571428571428572</v>
       </c>
       <c r="E2">
         <v>140</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
